--- a/experiment/test/results-Manga109/Manga109.xlsx
+++ b/experiment/test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.84</v>
+        <v>31.23</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8303</v>
+        <v>0.8858</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.15</v>
+        <v>33.03</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8163</v>
+        <v>0.8743</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.68</v>
+        <v>31.13</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8519</v>
+        <v>0.9156</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.11</v>
+        <v>38.92</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9488</v>
+        <v>0.9683</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.22</v>
+        <v>40.99</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9809</v>
+        <v>0.9849</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.64</v>
+        <v>32.9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9216</v>
+        <v>0.9492</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.94</v>
+        <v>36.32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9606</v>
+        <v>0.9719</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.62</v>
+        <v>30.01</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8995</v>
+        <v>0.9327</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.32</v>
+        <v>33.77</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9332</v>
+        <v>0.9583</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32.31</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9025</v>
+        <v>0.9305</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.68</v>
+        <v>33.64</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9566</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.7</v>
+        <v>31.11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8737</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.1</v>
+        <v>36.27</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9663</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.57</v>
+        <v>34.73</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9051</v>
+        <v>0.9293</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.93</v>
+        <v>32.95</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9218</v>
+        <v>0.9564</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.06</v>
+        <v>31.04</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9143</v>
+        <v>0.9504</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.91</v>
+        <v>34.46</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9628</v>
+        <v>0.9772</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.95</v>
+        <v>37.79</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9785</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.22</v>
+        <v>33.27</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9052</v>
+        <v>0.9358</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33.54</v>
+        <v>36.42</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9786</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.47</v>
+        <v>34.93</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9284</v>
+        <v>0.9528</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.46</v>
+        <v>34.94</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9391</v>
+        <v>0.9616</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.77</v>
+        <v>33.34</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9193</v>
+        <v>0.9488</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37.77</v>
+        <v>40.2</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9732</v>
+        <v>0.9807</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.28</v>
+        <v>32.35</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.57</v>
+        <v>34.25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9433</v>
+        <v>0.9649</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.09</v>
+        <v>40.89</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9795</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.01</v>
+        <v>33.96</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9356</v>
+        <v>0.9558</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.94</v>
+        <v>36.72</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9615</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.91</v>
+        <v>34.61</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9465</v>
+        <v>0.9653</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27.65</v>
+        <v>30.52</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9483</v>
+        <v>0.9684</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.59</v>
+        <v>31.37</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9415</v>
+        <v>0.9635</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.85</v>
+        <v>35.47</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8999</v>
+        <v>0.9409</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.96</v>
+        <v>30.68</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7498</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.81</v>
+        <v>29.08</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8783</v>
+        <v>0.9221</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32.08</v>
+        <v>34.67</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9165</v>
+        <v>0.9467</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28.08</v>
+        <v>29.83</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8704</v>
+        <v>0.8987000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.54</v>
+        <v>37.98</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9728</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35.46</v>
+        <v>38.4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9649</v>
+        <v>0.9772999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.83</v>
+        <v>31.29</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9117</v>
+        <v>0.9401</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.32</v>
+        <v>34.03</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8712</v>
+        <v>0.9185</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33.41</v>
+        <v>35.6</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9212</v>
+        <v>0.9502</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21.06</v>
+        <v>23.54</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7538</v>
+        <v>0.8515</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>36.1</v>
+        <v>39.2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9809</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.36</v>
+        <v>26.79</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.13</v>
+        <v>31.1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9094</v>
+        <v>0.9482</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34.97</v>
+        <v>37.17</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9552</v>
+        <v>0.9707</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27.2</v>
+        <v>30.07</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8728</v>
+        <v>0.9143</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29.3</v>
+        <v>32.26</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9247</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27</v>
+        <v>28.85</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7685</v>
+        <v>0.8229</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.97</v>
+        <v>33.37</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9502</v>
+        <v>0.9644</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.76</v>
+        <v>36.18</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.5</v>
+        <v>38.36</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9054</v>
+        <v>0.9314</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>36.17</v>
+        <v>38.71</v>
       </c>
       <c r="C55" t="n">
-        <v>0.966</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.89</v>
+        <v>24.87</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7401</v>
+        <v>0.8377</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33.43</v>
+        <v>36.1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9681</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32.35</v>
+        <v>34.9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9649</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32.8</v>
+        <v>35.4</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9507</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.94</v>
+        <v>25.85</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7749</v>
+        <v>0.8501</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>34.19</v>
+        <v>36.75</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9718</v>
+        <v>0.9799</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>32.42</v>
+        <v>35.69</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9519</v>
+        <v>0.9735</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.66</v>
+        <v>33.87</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9555</v>
+        <v>0.9694</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.76</v>
+        <v>37.69</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9707</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>34.3</v>
+        <v>36.54</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9296</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.8</v>
+        <v>28.98</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9411</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.62</v>
+        <v>35.71</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9448</v>
+        <v>0.9665</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>33.67</v>
+        <v>36.14</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9352</v>
+        <v>0.9572000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>32.48</v>
+        <v>35.04</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9654</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>28.71</v>
+        <v>31.35</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9293</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31.45</v>
+        <v>33.97</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9427</v>
+        <v>0.9628</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.06</v>
+        <v>29.32</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7655999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>35.16</v>
+        <v>37.91</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9608</v>
+        <v>0.9764</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>34.24</v>
+        <v>36.97</v>
       </c>
       <c r="C74" t="n">
-        <v>0.954</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.56</v>
+        <v>31.91</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8956</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29.96</v>
+        <v>32.26</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9066</v>
+        <v>0.9399</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.83</v>
+        <v>33.83</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9336</v>
+        <v>0.9537</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>30.43</v>
+        <v>33.49</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8823</v>
+        <v>0.9351</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28.44</v>
+        <v>29.9</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8142</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31.45</v>
+        <v>34.14</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9402</v>
+        <v>0.9651999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>31.41</v>
+        <v>34.47</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9467</v>
+        <v>0.9711</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>30.22</v>
+        <v>32.7</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8807</v>
+        <v>0.9235</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.27</v>
+        <v>34.78</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9077</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>32.1</v>
+        <v>35.17</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9624</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.99</v>
+        <v>31.04</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9675</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.84</v>
+        <v>35.78</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9373</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.66</v>
+        <v>30.79</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8791</v>
+        <v>0.9228</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>36.2</v>
+        <v>38.33</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9553</v>
+        <v>0.9704</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>34.31</v>
+        <v>36.67</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9644</v>
+        <v>0.9754</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30.82</v>
+        <v>33.09</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9274</v>
+        <v>0.9513</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.81</v>
+        <v>28.11</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8702</v>
+        <v>0.9058</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.28</v>
+        <v>32.22</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9218</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.48</v>
+        <v>29.57</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9497</v>
+        <v>0.9628</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>21.31</v>
+        <v>23.14</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.8322000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.2</v>
+        <v>37.41</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9569</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>27.08</v>
+        <v>29.5</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8893</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30.67</v>
+        <v>32.93</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9126</v>
+        <v>0.9399</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32.7</v>
+        <v>34.54</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8788</v>
+        <v>0.9177999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29.59</v>
+        <v>31.94</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9788</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.98</v>
+        <v>28.26</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7629</v>
+        <v>0.8446</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24</v>
+        <v>26.78</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8998</v>
+        <v>0.9349</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.57</v>
+        <v>29.82</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9071</v>
+        <v>0.9408</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>21.15</v>
+        <v>29.39</v>
       </c>
       <c r="C103" t="n">
-        <v>0.761</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>37.77</v>
+        <v>40.28</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9772</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>29.16</v>
+        <v>32.61</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9121</v>
+        <v>0.9454</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>34.41</v>
+        <v>36.09</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9784</v>
+        <v>0.9817</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>30</v>
+        <v>32.19</v>
       </c>
       <c r="C107" t="n">
-        <v>0.8937</v>
+        <v>0.9307</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>37.03</v>
+        <v>39.13</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9397</v>
+        <v>0.9574</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>31.72</v>
+        <v>34.19</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.75</v>
+        <v>32.69</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9225</v>
+        <v>0.9641999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>31</v>
+        <v>33.53</v>
       </c>
       <c r="C111" t="n">
-        <v>0.9141</v>
+        <v>0.9442</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-Manga109/Manga109.xlsx
+++ b/experiment/test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.63</v>
+        <v>28.48</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8219</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.02</v>
+        <v>30.95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8131</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.54</v>
+        <v>28.08</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8472</v>
+        <v>0.8424</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.07</v>
+        <v>35.91</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9478</v>
+        <v>0.9469</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.17</v>
+        <v>38.72</v>
       </c>
       <c r="C6" t="n">
-        <v>0.976</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.38</v>
+        <v>30.13</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9167</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.49</v>
+        <v>33.27</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9567</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.41</v>
+        <v>26.95</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8953</v>
+        <v>0.8893</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.02</v>
+        <v>30.68</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.9</v>
+        <v>29.28</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8984</v>
+        <v>0.8912</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.13</v>
+        <v>29.77</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9481000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.46</v>
+        <v>28.09</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8672</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.83</v>
+        <v>32.91</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9628</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.35</v>
+        <v>31.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9026</v>
+        <v>0.9002</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29.09</v>
+        <v>28.65</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9196</v>
+        <v>0.9153</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.89</v>
+        <v>27.78</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9086</v>
+        <v>0.9082</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.52</v>
+        <v>30.74</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.65</v>
+        <v>34.3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9766</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.01</v>
+        <v>30.97</v>
       </c>
       <c r="C20" t="n">
-        <v>0.903</v>
+        <v>0.9019</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33.13</v>
+        <v>32.71</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.18</v>
+        <v>31.63</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9182</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.22</v>
+        <v>31.63</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9351</v>
+        <v>0.9263</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.52</v>
+        <v>30.25</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9114</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37.45</v>
+        <v>36.9</v>
       </c>
       <c r="C25" t="n">
-        <v>0.971</v>
+        <v>0.9699</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.08</v>
+        <v>28.76</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9536</v>
+        <v>0.9539</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.37</v>
+        <v>31.11</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9401</v>
+        <v>0.9386</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38.57</v>
+        <v>38.09</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9766</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.63</v>
+        <v>31.59</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9316</v>
+        <v>0.9308</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.42</v>
+        <v>33.08</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9587</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.76</v>
+        <v>31.37</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9433</v>
+        <v>0.9405</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27.18</v>
+        <v>26.6</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9386</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.17</v>
+        <v>27.47</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9333</v>
+        <v>0.9236</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.74</v>
+        <v>32.46</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.88</v>
+        <v>28.56</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7411</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.69</v>
+        <v>26.34</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8734</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.93</v>
+        <v>31.49</v>
       </c>
       <c r="C37" t="n">
-        <v>0.914</v>
+        <v>0.9095</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.85</v>
+        <v>27.56</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8659</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.14</v>
+        <v>34.84</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9698</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35.18</v>
+        <v>35.03</v>
       </c>
       <c r="C40" t="n">
-        <v>0.962</v>
+        <v>0.9613</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.46</v>
+        <v>27.85</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9006</v>
+        <v>0.8901</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.02</v>
+        <v>30.6</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8676</v>
+        <v>0.8578</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33.02</v>
+        <v>32.86</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9156</v>
+        <v>0.9131</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21.09</v>
+        <v>20.83</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7476</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35.36</v>
+        <v>35.23</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9761</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.21</v>
+        <v>24.97</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9169</v>
+        <v>0.9156</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27.97</v>
+        <v>27.66</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9041</v>
+        <v>0.8987000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34.7</v>
+        <v>34.52</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9522</v>
+        <v>0.9503</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27.15</v>
+        <v>26.72</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8689</v>
+        <v>0.8604000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29.04</v>
+        <v>28.8</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9195</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.84</v>
+        <v>26.59</v>
       </c>
       <c r="C51" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.45</v>
+        <v>30.09</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9456</v>
+        <v>0.9436</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.43</v>
+        <v>33.12</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9453</v>
+        <v>0.9421</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.43</v>
+        <v>36.32</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35.72</v>
+        <v>35.63</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9623</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.84</v>
+        <v>22.65</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7321</v>
+        <v>0.7238</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33.1</v>
+        <v>33.04</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9643</v>
+        <v>0.9651</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.84</v>
+        <v>30.71</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9478</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32.35</v>
+        <v>31.54</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9452</v>
+        <v>0.9409</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.86</v>
+        <v>23.66</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7657</v>
+        <v>0.7571</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.72</v>
+        <v>33.45</v>
       </c>
       <c r="C61" t="n">
-        <v>0.969</v>
+        <v>0.9685</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.99</v>
+        <v>31.77</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9468</v>
+        <v>0.9443</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.25</v>
+        <v>30.72</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9505</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.19</v>
+        <v>34.84</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9659</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>34.04</v>
+        <v>33.83</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9272</v>
+        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.59</v>
+        <v>24.86</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9342</v>
+        <v>0.9226</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.42</v>
+        <v>31.87</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9407</v>
+        <v>0.9382</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>33.31</v>
+        <v>32.96</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9324</v>
+        <v>0.9294</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.97</v>
+        <v>31.69</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9418</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>28.46</v>
+        <v>28.26</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9223</v>
+        <v>0.9208</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31.13</v>
+        <v>30.67</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9381</v>
+        <v>0.9354</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.98</v>
+        <v>27.86</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7145</v>
+        <v>0.7104</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>34.85</v>
+        <v>34.81</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9585</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>34.09</v>
+        <v>33.84</v>
       </c>
       <c r="C74" t="n">
-        <v>0.952</v>
+        <v>0.9495</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.38</v>
+        <v>28.15</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8919</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29.8</v>
+        <v>29.53</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8978</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.66</v>
+        <v>30.3</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9312</v>
+        <v>0.9308</v>
       </c>
     </row>
     <row r="78">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>30.21</v>
+        <v>30.12</v>
       </c>
       <c r="C78" t="n">
         <v>0.878</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28.32</v>
+        <v>27.94</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8066</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31.25</v>
+        <v>30.89</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9363</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>31.18</v>
+        <v>30.93</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9424</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>30.16</v>
+        <v>29.87</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8764</v>
+        <v>0.8711</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.1</v>
+        <v>31.83</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9049</v>
+        <v>0.9023</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31.74</v>
+        <v>31.26</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9586</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.82</v>
+        <v>27.42</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9432</v>
+        <v>0.9414</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.58</v>
+        <v>32.18</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9332</v>
+        <v>0.9294</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.52</v>
+        <v>28.32</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8746</v>
+        <v>0.8724</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.71</v>
+        <v>35.35</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9518</v>
+        <v>0.9507</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>33.98</v>
+        <v>33.62</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9619</v>
+        <v>0.9606</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30.46</v>
+        <v>30.28</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9234</v>
+        <v>0.9207</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.58</v>
+        <v>24.97</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8636</v>
+        <v>0.8552</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.93</v>
+        <v>28.64</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9144</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.35</v>
+        <v>26.87</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9435</v>
+        <v>0.9432</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>21.2</v>
+        <v>20.95</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7418</v>
+        <v>0.7316</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.14</v>
+        <v>33.53</v>
       </c>
       <c r="C95" t="n">
-        <v>0.955</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.92</v>
+        <v>26.34</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8837</v>
+        <v>0.8777</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30.11</v>
+        <v>29.58</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9059</v>
+        <v>0.9039</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32.62</v>
+        <v>32.47</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8764</v>
+        <v>0.8751</v>
       </c>
     </row>
     <row r="99">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29.18</v>
+        <v>29.08</v>
       </c>
       <c r="C99" t="n">
         <v>0.9634</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.94</v>
+        <v>26.04</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7583</v>
+        <v>0.7606000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23.96</v>
+        <v>23.47</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8922</v>
+        <v>0.8851</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.45</v>
+        <v>27.22</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.8987000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>23.06</v>
+        <v>23.88</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8076</v>
+        <v>0.8481</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>36.75</v>
+        <v>36.69</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9716</v>
+        <v>0.9735</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>29.07</v>
+        <v>28.59</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9082</v>
+        <v>0.9056</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.64</v>
+        <v>32.57</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9731</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29.81</v>
+        <v>29.52</v>
       </c>
       <c r="C107" t="n">
-        <v>0.8888</v>
+        <v>0.8858</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>37.04</v>
+        <v>37.01</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9386</v>
+        <v>0.9379</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>31.72</v>
+        <v>31.58</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8632</v>
+        <v>0.8604000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.61</v>
+        <v>28.19</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9161</v>
+        <v>0.9069</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30.75</v>
+        <v>30.41</v>
       </c>
       <c r="C111" t="n">
-        <v>0.9101</v>
+        <v>0.9072</v>
       </c>
     </row>
   </sheetData>
